--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES I-X/FRACC X/LTAIPT_A63F10A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES I-X/FRACC X/LTAIPT_A63F10A.xlsx
@@ -4,23 +4,25 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
     <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
+    <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Hidden_17">Hidden_1!$A$1:$A$6</definedName>
     <definedName name="Hidden_29">Hidden_2!$A$1:$A$2</definedName>
+    <definedName name="Hidden_310">Hidden_3!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="83">
   <si>
     <t>48956</t>
   </si>
@@ -88,6 +90,9 @@
     <t>435854</t>
   </si>
   <si>
+    <t>571914</t>
+  </si>
+  <si>
     <t>435855</t>
   </si>
   <si>
@@ -118,7 +123,7 @@
     <t>Denominación del área</t>
   </si>
   <si>
-    <t>Denominación del puesto</t>
+    <t>Denominación del puesto (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Clave o nivel de puesto</t>
@@ -133,7 +138,10 @@
     <t>Por cada puesto y/o cargo de la estructura especificar el estado (catálogo)</t>
   </si>
   <si>
-    <t>Hipervínculo a las convocatorias a concursos para ocupar cargos públicos</t>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
+    <t>Por cada puesto y/o cargo de la estructura vacante se incluirá un hipervínculo a las convocatorias a concursos para ocupar cargos públicos (Redactadas con perspectiva de género)</t>
   </si>
   <si>
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
@@ -148,13 +156,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>Jefatura de materia</t>
-  </si>
-  <si>
-    <t>Jefe de materia</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Directivo</t>
@@ -163,9 +165,6 @@
     <t>Confianza</t>
   </si>
   <si>
-    <t>Subdirección académica</t>
-  </si>
-  <si>
     <t>Vacante</t>
   </si>
   <si>
@@ -175,97 +174,79 @@
     <t>Departamento de Recursos Humanos</t>
   </si>
   <si>
-    <t>Subdirección de plantel B</t>
-  </si>
-  <si>
-    <t>Subdirector de plantel</t>
-  </si>
-  <si>
-    <t>Plantel 18 Atltzayanca</t>
-  </si>
-  <si>
-    <t>Plantel 17 Cuapiaxtla</t>
+    <t>Jefatura de Departamento</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento</t>
+  </si>
+  <si>
+    <t>Plantel 03 Calpulalpan</t>
+  </si>
+  <si>
+    <t>F2570545BFBEAC01404A8300B9492A7C</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>Subdirección de Plantel C</t>
+  </si>
+  <si>
+    <t>Subdirector de Plantel C</t>
+  </si>
+  <si>
+    <t>Plantel 06 Contla</t>
+  </si>
+  <si>
+    <t>13/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de julio de 2023 al 30 de septiembre de 2023, en el Colegio de Bachilleres del Estado de Tlaxcala, las plazas vacantes no son concursables  debido a que son plazas directivas.  El sexo de las vacantes es indistinto.</t>
+  </si>
+  <si>
+    <t>FC25C5C3A60D29202FB2C55C644D6ED4</t>
+  </si>
+  <si>
+    <t>54EC189A86D19D65ED4C9EF2DB2EFCC1</t>
+  </si>
+  <si>
+    <t>Subdirección de Servicios Administrativos</t>
+  </si>
+  <si>
+    <t>Subdirector de Área</t>
+  </si>
+  <si>
+    <t>4D62B403497518EF91E6AAB15D5A2EE9</t>
+  </si>
+  <si>
+    <t>Subdirección de Plantel B</t>
+  </si>
+  <si>
+    <t>Subdirector de Plantel B</t>
   </si>
   <si>
     <t>Plantel 09 Tlaxco</t>
   </si>
   <si>
-    <t>Subdirección de plantel C</t>
-  </si>
-  <si>
-    <t>Jefatura de Departamento</t>
-  </si>
-  <si>
-    <t>7130715EA91B49308C4C2A8607642913</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>17/10/2022</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de julio de 2022 al 30 de septiembre de 2022, en el Colegio de Bachilleres del Estado de Tlaxcala, las plazas vacantes no son concursables  debido a que son plazas directivas.</t>
-  </si>
-  <si>
-    <t>2DDB21A57E4AFF2118AD9F821B2B1FB5</t>
-  </si>
-  <si>
-    <t>Plantel 24 Tizatlan</t>
-  </si>
-  <si>
-    <t>C4FDA2E7567FB5F5AD8AE33512D9428F</t>
-  </si>
-  <si>
-    <t>5979CC555055D741A4B253EEE1027CBF</t>
-  </si>
-  <si>
-    <t>A68321D237FC5F60DA408883742072B5</t>
-  </si>
-  <si>
-    <t>C764C272CF9B01E4EC5A9DF0FF6E15F2</t>
-  </si>
-  <si>
-    <t>Subdirección del Plantel 05 Panzacola</t>
-  </si>
-  <si>
-    <t>D86FD0FE23822AD176826FCAA350CA9B</t>
-  </si>
-  <si>
-    <t>Subdirección del Plantel 01 Tlaxcala</t>
-  </si>
-  <si>
-    <t>B3450354485CAE242A44DA2040D3E00E</t>
-  </si>
-  <si>
-    <t>Dirección de plantel A</t>
-  </si>
-  <si>
-    <t>Director de ploantel</t>
-  </si>
-  <si>
-    <t>Dirección del plantel 21 Ayometla</t>
-  </si>
-  <si>
-    <t>9402CBFD0F7B5C8E7BFF7B2430760F82</t>
-  </si>
-  <si>
-    <t>Jefe de departamento</t>
-  </si>
-  <si>
-    <t>Departamento de Recursos Materiales y Servicios Generales</t>
-  </si>
-  <si>
-    <t>F6CBCE1DAC7BEE1EB4F70E194B7D3054</t>
-  </si>
-  <si>
-    <t>Directorección Académica</t>
-  </si>
-  <si>
-    <t>Director Académico</t>
+    <t>A1056E66465FF34EDAF68D4A7DF64BB1</t>
+  </si>
+  <si>
+    <t>Departamento de Formación y Desarrollo Docente</t>
+  </si>
+  <si>
+    <t>2AB3068423FDCBD7F063316511400DD9</t>
+  </si>
+  <si>
+    <t>Jefatura de Materia</t>
+  </si>
+  <si>
+    <t>Jefe de Materia</t>
+  </si>
+  <si>
+    <t>Subdirección de Servicio Academico</t>
   </si>
   <si>
     <t>Permanente</t>
@@ -284,6 +265,12 @@
   </si>
   <si>
     <t>Ocupado</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
 </sst>
 </file>
@@ -676,32 +663,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="56.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="63.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="62.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="171.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="151.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="201.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -718,7 +706,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -733,7 +721,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -762,22 +750,25 @@
         <v>8</v>
       </c>
       <c r="K4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" t="s">
         <v>9</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>10</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>7</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>11</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -820,10 +811,13 @@
       <c r="O5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -839,69 +833,73 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
-    </row>
-    <row r="7" spans="1:15" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="P6" s="4"/>
+    </row>
+    <row r="7" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>45</v>
@@ -910,45 +908,48 @@
         <v>46</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="B9" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>45</v>
@@ -957,45 +958,48 @@
         <v>46</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>45</v>
@@ -1004,45 +1008,48 @@
         <v>46</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="J10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="N10" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>45</v>
@@ -1051,45 +1058,48 @@
         <v>46</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L11" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="M11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>45</v>
@@ -1098,45 +1108,48 @@
         <v>46</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>45</v>
@@ -1145,218 +1158,33 @@
         <v>46</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="L13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="N13" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="P13" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A6:P6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1364,12 +1192,15 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H169">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H194">
       <formula1>Hidden_17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J169">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J194">
       <formula1>Hidden_29</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8:K194">
+      <formula1>Hidden_310</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1383,17 +1214,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -1403,12 +1234,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1423,12 +1254,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
